--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/00679B-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/00679B-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9CC20ED8-BA9A-427E-BBEA-5D5B057BD65A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{271CDFFB-CCBD-4ED1-B9CD-714CEDF956C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{02B781E1-03E5-401D-91AE-A451B54AA2B7}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{C4B2C350-CACC-49EE-9829-FC7992F472FE}"/>
   </bookViews>
   <sheets>
     <sheet name="00679B-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1651,25 +1651,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8043BB5F-BC30-4139-916A-F5EC0C2AD4BE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E4AADE1-F1CE-4199-B945-B6FF53A3F6E2}">
   <dimension ref="A1:R51"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.44140625" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="10.625" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="5" max="5" width="9.875" customWidth="1"/>
+    <col min="6" max="6" width="10.375" customWidth="1"/>
+    <col min="7" max="9" width="9.875" customWidth="1"/>
+    <col min="10" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1697,7 +1697,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1727,7 +1727,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1773,7 +1773,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1823,7 +1823,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2026</v>
       </c>
@@ -1877,7 +1877,7 @@
         <v>4.0199999999999996</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="41"/>
       <c r="B6" s="42"/>
       <c r="C6" s="44"/>
@@ -1903,7 +1903,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>27</v>
       </c>
@@ -1959,7 +1959,7 @@
         <v>1.01</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="49">
         <v>2025</v>
       </c>
@@ -2013,7 +2013,7 @@
         <v>4.4000000000000004</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
         <v>27</v>
       </c>
@@ -2069,7 +2069,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>27</v>
       </c>
@@ -2125,7 +2125,7 @@
         <v>1.08</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>27</v>
       </c>
@@ -2181,7 +2181,7 @@
         <v>1.26</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>27</v>
       </c>
@@ -2237,7 +2237,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="51">
         <v>2024</v>
       </c>
@@ -2291,7 +2291,7 @@
         <v>4.42</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>27</v>
       </c>
@@ -2347,7 +2347,7 @@
         <v>1.17</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>27</v>
       </c>
@@ -2403,7 +2403,7 @@
         <v>1.0900000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>27</v>
       </c>
@@ -2459,7 +2459,7 @@
         <v>1.1299999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>27</v>
       </c>
@@ -2515,7 +2515,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="49">
         <v>2023</v>
       </c>
@@ -2569,7 +2569,7 @@
         <v>3.77</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
         <v>27</v>
       </c>
@@ -2625,7 +2625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
         <v>27</v>
       </c>
@@ -2681,7 +2681,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
         <v>27</v>
       </c>
@@ -2737,7 +2737,7 @@
         <v>0.89</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="19" t="s">
         <v>27</v>
       </c>
@@ -2793,7 +2793,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="51">
         <v>2022</v>
       </c>
@@ -2847,7 +2847,7 @@
         <v>3.27</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>27</v>
       </c>
@@ -2903,7 +2903,7 @@
         <v>1.08</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>27</v>
       </c>
@@ -2959,7 +2959,7 @@
         <v>0.83</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>27</v>
       </c>
@@ -3015,7 +3015,7 @@
         <v>0.78</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>27</v>
       </c>
@@ -3071,7 +3071,7 @@
         <v>0.59</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="49">
         <v>2021</v>
       </c>
@@ -3125,7 +3125,7 @@
         <v>2.13</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="19" t="s">
         <v>27</v>
       </c>
@@ -3181,7 +3181,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
         <v>27</v>
       </c>
@@ -3237,7 +3237,7 @@
         <v>0.52</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="19" t="s">
         <v>27</v>
       </c>
@@ -3293,7 +3293,7 @@
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
         <v>27</v>
       </c>
@@ -3349,7 +3349,7 @@
         <v>0.52</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="51">
         <v>2020</v>
       </c>
@@ -3403,7 +3403,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
         <v>27</v>
       </c>
@@ -3459,7 +3459,7 @@
         <v>0.43</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
         <v>27</v>
       </c>
@@ -3515,7 +3515,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
         <v>27</v>
       </c>
@@ -3571,7 +3571,7 @@
         <v>0.31</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
         <v>27</v>
       </c>
@@ -3627,7 +3627,7 @@
         <v>0.51</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="49">
         <v>2019</v>
       </c>
@@ -3681,7 +3681,7 @@
         <v>2.4900000000000002</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="19" t="s">
         <v>27</v>
       </c>
@@ -3737,7 +3737,7 @@
         <v>0.56999999999999995</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="19" t="s">
         <v>27</v>
       </c>
@@ -3793,7 +3793,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="19" t="s">
         <v>27</v>
       </c>
@@ -3849,7 +3849,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="19" t="s">
         <v>27</v>
       </c>
@@ -3905,7 +3905,7 @@
         <v>0.67</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="51">
         <v>2018</v>
       </c>
@@ -3959,7 +3959,7 @@
         <v>2.64</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="11" t="s">
         <v>27</v>
       </c>
@@ -4015,7 +4015,7 @@
         <v>0.67</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="11" t="s">
         <v>27</v>
       </c>
@@ -4071,7 +4071,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="11" t="s">
         <v>27</v>
       </c>
@@ -4127,7 +4127,7 @@
         <v>0.57999999999999996</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="11" t="s">
         <v>27</v>
       </c>
@@ -4183,7 +4183,7 @@
         <v>0.69</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="49">
         <v>2017</v>
       </c>
@@ -4237,7 +4237,7 @@
         <v>1.86</v>
       </c>
     </row>
-    <row r="49" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="19" t="s">
         <v>27</v>
       </c>
@@ -4293,7 +4293,7 @@
         <v>0.71</v>
       </c>
     </row>
-    <row r="50" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="19" t="s">
         <v>27</v>
       </c>
@@ -4349,7 +4349,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="51" t="s">
         <v>88</v>
       </c>
